--- a/casos de prueba/suite_automatizacion_everest.xlsx
+++ b/casos de prueba/suite_automatizacion_everest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://everisgroup-my.sharepoint.com/personal/dnarvaec_emeal_nttdata_com1/Documents/Documents/Proyectos AUTO/Demos Comerciales/demo-servicios-axet-plugin/casos de prueba/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://everisgroup-my.sharepoint.com/personal/dnarvaec_emeal_nttdata_com1/Documents/Documents/Proyectos AUTO/Everest/auto-api-axet-plugin/demo-servicios-axet-plugin/casos de prueba/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_95F9D6A7D30C7B4485719F96358FC215515D138E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C6D73B1-9A19-403F-9A71-16C343514C47}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_F4478A45D67C223E6858C0F55389D63980D4064D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C20A504-C354-410A-A4F2-5D3932D28960}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,6 +61,9 @@
     <t>Actor autorizado en API de retiros | CallAnApi.at(BASE) | X-RqUID=001001, X-Channel=ATM, X-CompanyId=BANCO_BOGOTA, X-CustIdentType=CC, X-CustIdentNum=123456789</t>
   </si>
   <si>
+    <t>Pass</t>
+  </si>
+  <si>
     <t>POST https://api.aval.nttdataco.com/api/v1/pagos/retiro
 Headers: X-RqUID=001001 | X-Channel=ATM | X-CompanyId=BANCO_BOGOTA | X-CustIdentNum=123456789
 Tags: @smoke @e2e @tx01 @retiro
@@ -397,9 +400,6 @@
   <si>
     <t>PASO 1: HTTP 200 | msgRsHdr.status.statusCode='200' | data.Agreement.Name!=null | data.TotalCurAmt.Amt!=null
 PASO 2: HTTP 200 | msgRsHdr.status.severity='Info' | msgRsHdr.status.statusDesc='Transaccion exitosa' | endDt!=null</t>
-  </si>
-  <si>
-    <t>Pass</t>
   </si>
 </sst>
 </file>
@@ -855,16 +855,16 @@
         <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -875,25 +875,25 @@
         <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -904,25 +904,25 @@
         <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -933,25 +933,25 @@
         <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -962,25 +962,25 @@
         <v>9</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -991,25 +991,25 @@
         <v>9</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -1020,25 +1020,25 @@
         <v>9</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="I8" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -1049,25 +1049,25 @@
         <v>9</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -1078,25 +1078,25 @@
         <v>9</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -1107,25 +1107,25 @@
         <v>9</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -1136,25 +1136,25 @@
         <v>9</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -1165,25 +1165,25 @@
         <v>9</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -1194,25 +1194,25 @@
         <v>9</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -1223,34 +1223,28 @@
         <v>9</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{3048dc87-43f0-4100-9acb-ae1971c79395}" enabled="0" method="" siteId="{3048dc87-43f0-4100-9acb-ae1971c79395}" removed="1"/>
-</clbl:labelList>
 </file>